--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104590_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104590_W15.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1114</v>
+        <v>4.5722</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7548</v>
+        <v>1.5005</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3565</v>
+        <v>3.0717</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3012</v>
+        <v>4.3022</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5339</v>
+        <v>2.5278</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7673</v>
+        <v>1.7744</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8743</v>
+        <v>2.8501</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5038</v>
+        <v>2.4854</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3705</v>
+        <v>0.3647</v>
       </c>
       <c r="M2" t="n">
-        <v>1.4269</v>
+        <v>1.4522</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3968</v>
+        <v>1.4097</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3791</v>
+        <v>-0.1626</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2642</v>
+        <v>0.039</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1149</v>
+        <v>-0.2016</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.1568</v>
+        <v>-1.1609</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.1568</v>
+        <v>-1.1609</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5655</v>
+        <v>2.9407</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8812</v>
+        <v>0.8407</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6843</v>
+        <v>2.0999</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3871</v>
+        <v>0.9523</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1284</v>
+        <v>0.3592</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2586</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>1.415</v>
+        <v>1.336</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2787</v>
+        <v>0.1444</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.8637</v>
+        <v>1.1916</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.028</v>
+        <v>-0.3836</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1503</v>
+        <v>0.2148</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1223</v>
+        <v>-0.5984</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0177</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1202</v>
+        <v>-0.4952</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1024</v>
+        <v>0.5032</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7071</v>
+        <v>0.387</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6956</v>
+        <v>2.6238</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9055</v>
+        <v>1.4364</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7901</v>
+        <v>1.1874</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9487</v>
+        <v>1.393</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3622</v>
+        <v>1.126</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5865</v>
+        <v>0.267</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3531</v>
+        <v>1.3895</v>
       </c>
       <c r="K4" t="n">
-        <v>0.159</v>
+        <v>2.2613</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1941</v>
+        <v>-0.8718</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4044</v>
+        <v>0.0035</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2033</v>
+        <v>-1.1353</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6077</v>
+        <v>1.1388</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2265</v>
+        <v>0.073</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4476</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2211</v>
+        <v>-0.6372</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3856</v>
+        <v>0.7025</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0159</v>
+        <v>1.2879</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2353</v>
+        <v>0.4632</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7806</v>
+        <v>0.8247</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.149</v>
+        <v>-0.1419</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5036</v>
+        <v>-0.5027</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.44</v>
+        <v>-0.4449</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.44</v>
+        <v>-0.4449</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.291</v>
+        <v>0.303</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8351</v>
+        <v>-0.5702</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4174</v>
+        <v>-0.1813</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4177</v>
+        <v>-0.3888</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8355</v>
+        <v>0.7423</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0359</v>
+        <v>-0.2451</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8713</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.6555</v>
+        <v>0.2932</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4099</v>
+        <v>-1.2322</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.0654</v>
+        <v>1.5254</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2011</v>
+        <v>0.1899</v>
       </c>
       <c r="K6" t="n">
-        <v>1.198</v>
+        <v>-0.614</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.3991</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4543</v>
+        <v>0.1033</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.788</v>
+        <v>-0.6182</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6663</v>
+        <v>0.7215</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7424</v>
+        <v>0.2426</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3902</v>
+        <v>-0.3651</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3522</v>
+        <v>0.6077</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1607</v>
+        <v>-0.9317</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.2249</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3856</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X. LOPEZ-AROSTEGUI</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1474</v>
+        <v>0.1335</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2533</v>
+        <v>-1.4254</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4007</v>
+        <v>1.5589</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4914</v>
+        <v>-2.6663</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6464</v>
+        <v>0.4025</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.1378</v>
+        <v>-3.0688</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0179</v>
+        <v>-1.2352</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8832</v>
+        <v>1.1786</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.901</v>
+        <v>-2.4138</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4735</v>
+        <v>-1.431</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2368</v>
+        <v>-0.7761</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2368</v>
+        <v>-0.6549</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.5934</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>1.478</v>
+        <v>1.0486</v>
       </c>
       <c r="T7" t="n">
-        <v>0.738</v>
+        <v>0.039</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7401</v>
+        <v>1.0096</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>-0.2292</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>X. LOPEZ-AROSTEGUI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1997</v>
+        <v>-0.5904</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8092</v>
+        <v>-0.79</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6095</v>
+        <v>0.1996</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2909</v>
+        <v>-1.4902</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2338</v>
+        <v>0.649</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5247</v>
+        <v>-2.1391</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2126</v>
+        <v>-0.0299</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.603</v>
+        <v>0.8791</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8156</v>
+        <v>-0.909</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0784</v>
+        <v>-1.4603</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6308</v>
+        <v>-0.2301</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7091</v>
+        <v>-1.2301</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1342</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6929</v>
+        <v>0.742</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9557</v>
+        <v>0.2203</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2628</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7332</v>
+        <v>-1.1837</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6189</v>
+        <v>-2.7557</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8857</v>
+        <v>1.572</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5471</v>
+        <v>-2.553</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3822</v>
+        <v>-1.3897</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1648</v>
+        <v>-1.1633</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5241</v>
+        <v>-2.5578</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3964</v>
+        <v>-1.4176</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1276</v>
+        <v>-1.1401</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.023</v>
+        <v>0.0048</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0372</v>
+        <v>-0.0232</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0008</v>
+        <v>-0.4517</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0948</v>
+        <v>-0.1979</v>
       </c>
       <c r="U9" t="n">
-        <v>0.094</v>
+        <v>-0.2538</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.377</v>
+        <v>-3.2629</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6541</v>
+        <v>-2.546</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7229</v>
+        <v>-0.7169</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.943</v>
+        <v>-1.9461</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7271</v>
+        <v>-1.7316</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5381</v>
+        <v>-1.5448</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5381</v>
+        <v>-1.5448</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.405</v>
+        <v>-0.4012</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1391</v>
+        <v>-0.021</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0181</v>
+        <v>0.137</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1573</v>
+        <v>-0.1579</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.137</v>
+        <v>-3.7133</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.579</v>
+        <v>-7.093</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5580000000000001</v>
+        <v>3.3797</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6103</v>
+        <v>-3.0535</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6854</v>
+        <v>-5.0886</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9249000000000001</v>
+        <v>2.0351</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6464</v>
+        <v>-4.0611</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8974</v>
+        <v>-4.2692</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.749</v>
+        <v>0.2081</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9639</v>
+        <v>1.0076</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.788</v>
+        <v>-0.8194</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1759</v>
+        <v>1.827</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.2045</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7984</v>
+        <v>-0.5279</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1376</v>
+        <v>0.3234</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3433</v>
+        <v>-3.7354</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.872</v>
+        <v>-3.3601</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5287</v>
+        <v>-0.3753</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.0476</v>
+        <v>-2.6051</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.0761</v>
+        <v>-1.6832</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0285</v>
+        <v>-0.9219000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.0219</v>
+        <v>-1.6595</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.2404</v>
+        <v>-0.907</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2185</v>
+        <v>-0.7524</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9743000000000001</v>
+        <v>-0.9457</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8357</v>
+        <v>-0.7761</v>
       </c>
       <c r="O12" t="n">
-        <v>1.81</v>
+        <v>-0.1695</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.842</v>
+        <v>-0.2685</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3549</v>
+        <v>-0.5625</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5129</v>
+        <v>0.294</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.581</v>
+        <v>-5.4629</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.5061</v>
+        <v>-6.546</v>
       </c>
       <c r="F13" t="n">
-        <v>0.925</v>
+        <v>1.0831</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.1475</v>
+        <v>-2.1566</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3954</v>
+        <v>0.3909</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.5429</v>
+        <v>-2.5474</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.9672</v>
+        <v>-2.0034</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6958</v>
+        <v>0.6787</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.663</v>
+        <v>-2.6822</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1803</v>
+        <v>-0.1532</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3003</v>
+        <v>-0.2879</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1201</v>
+        <v>0.1347</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6435</v>
+        <v>-0.5064</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3217</v>
+        <v>-0.3071</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3218</v>
+        <v>-0.1994</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.999899999999998</v>
+        <v>-5.648200000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-20.5517</v>
+        <v>-20.5205</v>
       </c>
       <c r="F14" t="n">
-        <v>14.5515</v>
+        <v>14.8722</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.663500000000001</v>
+        <v>-9.672000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.132</v>
+        <v>-6.172599999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.5315</v>
+        <v>-3.499</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.5017</v>
+        <v>-7.7711</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.396799999999999</v>
+        <v>-1.57</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.104699999999999</v>
+        <v>-6.201000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1618</v>
+        <v>-1.9006</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.735</v>
+        <v>-4.602499999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5731</v>
+        <v>2.702</v>
       </c>
       <c r="P14" t="n">
-        <v>4.536500000000001</v>
+        <v>4.552599999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.4759</v>
+        <v>-12.5198</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0125</v>
+        <v>17.0725</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4235000000000002</v>
+        <v>-0.07080000000000014</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.8598</v>
+        <v>-1.4915</v>
       </c>
       <c r="U14" t="n">
-        <v>1.436399999999999</v>
+        <v>1.4209</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4498000000000001</v>
+        <v>-0.4583000000000002</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2858</v>
+        <v>1.2622</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7356</v>
+        <v>-1.7206</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0417</v>
+        <v>6.6339</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2027</v>
+        <v>5.2272</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8391</v>
+        <v>1.4067</v>
       </c>
       <c r="G15" t="n">
-        <v>5.5513</v>
+        <v>5.5377</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9711</v>
+        <v>2.9671</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5802</v>
+        <v>2.5707</v>
       </c>
       <c r="J15" t="n">
-        <v>5.1584</v>
+        <v>5.1185</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8155</v>
+        <v>2.7956</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3428</v>
+        <v>2.3229</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3929</v>
+        <v>0.4192</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1556</v>
+        <v>0.1715</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2315</v>
+        <v>0.3646</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9557</v>
+        <v>0.1087</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2758</v>
+        <v>0.2559</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9388</v>
+        <v>2.0181</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2948</v>
+        <v>1.3915</v>
       </c>
       <c r="F16" t="n">
-        <v>0.644</v>
+        <v>0.6266</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3979</v>
+        <v>-1.402</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3073</v>
+        <v>-1.3095</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0906</v>
+        <v>-0.0924</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9135</v>
+        <v>-0.9285</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7242</v>
+        <v>-0.7347</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1893</v>
+        <v>-0.1939</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4844</v>
+        <v>-0.4734</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O16" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6296</v>
+        <v>1.7176</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9549</v>
+        <v>1.0728</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6747</v>
+        <v>0.6448</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2923</v>
+        <v>1.9507</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7651</v>
+        <v>-0.4194</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0574</v>
+        <v>2.3701</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7053</v>
+        <v>1.723</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1801</v>
+        <v>1.194</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5251</v>
+        <v>0.529</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2087</v>
+        <v>0.2011</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8832</v>
+        <v>0.8791</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4965</v>
+        <v>1.5219</v>
       </c>
       <c r="N17" t="n">
-        <v>0.297</v>
+        <v>0.3149</v>
       </c>
       <c r="O17" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5471</v>
+        <v>0.0896</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9739</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4267</v>
+        <v>0.7101</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1826</v>
+        <v>1.1241</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0979</v>
+        <v>-0.1133</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2805</v>
+        <v>1.2374</v>
       </c>
       <c r="G18" t="n">
-        <v>1.052</v>
+        <v>1.0566</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3074</v>
+        <v>-0.3019</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3594</v>
+        <v>1.3585</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8246</v>
+        <v>0.8114</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1803</v>
+        <v>-0.1864</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0048</v>
+        <v>0.9977</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2274</v>
+        <v>0.2452</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.323</v>
+        <v>-0.3878</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6956</v>
+        <v>-0.697</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3726</v>
+        <v>0.3093</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. TILLIE</t>
+          <t>J. WEBB III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4768</v>
+        <v>0.8882</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0801</v>
+        <v>-2.1766</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5568</v>
+        <v>3.0649</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3409</v>
+        <v>1.2565</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1732</v>
+        <v>0.0829</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5141</v>
+        <v>1.1736</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.1738</v>
+        <v>0.1652</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1079</v>
+        <v>-0.1174</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.066</v>
+        <v>0.2826</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8329</v>
+        <v>1.0914</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2811</v>
+        <v>0.2003</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.8911</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1391</v>
+        <v>0.3845</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3206</v>
+        <v>-0.2232</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1815</v>
+        <v>0.6077</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7712</v>
+        <v>0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. WEBB III</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.011</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6211</v>
+        <v>-1.5692</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6321</v>
+        <v>1.6377</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2545</v>
+        <v>-0.3873</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0764</v>
+        <v>0.0429</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1781</v>
+        <v>-0.4302</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1821</v>
+        <v>-1.1368</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.111</v>
+        <v>-0.4589</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2931</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0724</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1874</v>
+        <v>0.5018</v>
       </c>
       <c r="O20" t="n">
-        <v>0.885</v>
+        <v>0.2477</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4969</v>
+        <v>-0.5457</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6956</v>
+        <v>-0.4324</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1987</v>
+        <v>-0.1133</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1607</v>
+        <v>0.7739</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>K. TILLIE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0569</v>
+        <v>-0.2372</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4223</v>
+        <v>-2.8282</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3655</v>
+        <v>2.591</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5747</v>
+        <v>-1.3504</v>
       </c>
       <c r="H21" t="n">
-        <v>2.4068</v>
+        <v>0.1724</v>
       </c>
       <c r="I21" t="n">
-        <v>0.168</v>
+        <v>-1.5228</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3845</v>
+        <v>-2.2145</v>
       </c>
       <c r="K21" t="n">
-        <v>1.9843</v>
+        <v>-0.1281</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5998</v>
+        <v>-2.0864</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1902</v>
+        <v>0.8641</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4224</v>
+        <v>0.3005</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7678</v>
+        <v>0.5636</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.4025</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.5367</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4494</v>
+        <v>-0.5713</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4083</v>
+        <v>-0.386</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0411</v>
+        <v>-0.1852</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3214</v>
+        <v>0.7739</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. DUARTE</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.311</v>
+        <v>-0.2891</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7185</v>
+        <v>-2.8148</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4075</v>
+        <v>2.5257</v>
       </c>
       <c r="G22" t="n">
-        <v>0.851</v>
+        <v>2.5868</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0994</v>
+        <v>2.4122</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7516</v>
+        <v>0.1746</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2504</v>
+        <v>1.3648</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0693</v>
+        <v>1.9683</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1812</v>
+        <v>-0.6035</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6006</v>
+        <v>1.222</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0301</v>
+        <v>0.444</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5705</v>
+        <v>0.778</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.0415</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-4.5526</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4939</v>
+        <v>0.223</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2994</v>
+        <v>0.0575</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1945</v>
+        <v>0.1655</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3856</v>
+        <v>0.3155</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>C. DUARTE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4774</v>
+        <v>-0.5614</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0258</v>
+        <v>-2.2086</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5484</v>
+        <v>1.6471</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3982</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0389</v>
+        <v>0.1114</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4371</v>
+        <v>0.746</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1215</v>
+        <v>0.2398</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4471</v>
+        <v>0.0689</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6744</v>
+        <v>0.1708</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.6176</v>
       </c>
       <c r="N23" t="n">
-        <v>0.486</v>
+        <v>0.0424</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2373</v>
+        <v>0.5752</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2268</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0773</v>
+        <v>0.2429</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9043</v>
+        <v>-0.1721</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.173</v>
+        <v>0.4149</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7712</v>
+        <v>0.387</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.7712</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>K. PERRY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-1.2026</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1829</v>
+        <v>-2.7675</v>
       </c>
       <c r="F24" t="n">
-        <v>2.2671</v>
+        <v>1.5649</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1193</v>
+        <v>0.7681</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6177</v>
+        <v>-0.8358</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4984</v>
+        <v>1.6038</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2703</v>
+        <v>0.7357</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3668</v>
+        <v>-0.8348</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6371</v>
+        <v>1.5705</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3896</v>
+        <v>0.0324</v>
       </c>
       <c r="N24" t="n">
-        <v>0.251</v>
+        <v>-0.0009</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1387</v>
+        <v>0.0333</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5878</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.4952</v>
+        <v>-3.6421</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7134</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4174</v>
+        <v>0.1389</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1308</v>
+        <v>-0.1308</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>K. PERRY</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.6423</v>
+        <v>-1.4002</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9532</v>
+        <v>-3.0932</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3109</v>
+        <v>1.693</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7798</v>
+        <v>0.115</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8355</v>
+        <v>0.6093</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6152</v>
+        <v>-0.4944</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7759</v>
+        <v>-0.2895</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.8179</v>
+        <v>0.3512</v>
       </c>
       <c r="L25" t="n">
-        <v>1.5938</v>
+        <v>-0.6407</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0038</v>
+        <v>0.4044</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0176</v>
+        <v>0.2581</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0214</v>
+        <v>0.1463</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.8147</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.6293</v>
+        <v>-2.5039</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4467</v>
+        <v>0.236</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0998</v>
+        <v>-0.2998</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3469</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.5397</v>
+        <v>-1.417</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.1822</v>
+        <v>-3.5001</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6425</v>
+        <v>2.0831</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.0873</v>
+        <v>-1.0895</v>
       </c>
       <c r="H26" t="n">
-        <v>1.0186</v>
+        <v>1.0277</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.1059</v>
+        <v>-2.1172</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.1438</v>
+        <v>-2.1665</v>
       </c>
       <c r="K26" t="n">
-        <v>1.0044</v>
+        <v>0.9997</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.1481</v>
+        <v>-3.1662</v>
       </c>
       <c r="M26" t="n">
-        <v>1.0565</v>
+        <v>1.077</v>
       </c>
       <c r="N26" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O26" t="n">
-        <v>1.0423</v>
+        <v>1.049</v>
       </c>
       <c r="P26" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R26" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8794999999999999</v>
+        <v>0.2369</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6775</v>
+        <v>0.0322</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.202</v>
+        <v>0.2047</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>6.000099999999998</v>
+        <v>7.576099999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-14.5516</v>
+        <v>-14.8722</v>
       </c>
       <c r="F27" t="n">
-        <v>20.5518</v>
+        <v>22.4482</v>
       </c>
       <c r="G27" t="n">
-        <v>9.663600000000002</v>
+        <v>9.671900000000003</v>
       </c>
       <c r="H27" t="n">
-        <v>6.132000000000001</v>
+        <v>6.1727</v>
       </c>
       <c r="I27" t="n">
-        <v>3.531499999999999</v>
+        <v>3.4992</v>
       </c>
       <c r="J27" t="n">
-        <v>2.1617</v>
+        <v>1.9007</v>
       </c>
       <c r="K27" t="n">
-        <v>4.735100000000001</v>
+        <v>4.602499999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.573399999999999</v>
+        <v>-2.701999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>7.5017</v>
+        <v>7.7713</v>
       </c>
       <c r="N27" t="n">
-        <v>1.3969</v>
+        <v>1.5702</v>
       </c>
       <c r="O27" t="n">
-        <v>6.104900000000001</v>
+        <v>6.201000000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>-4.5366</v>
+        <v>-4.5526</v>
       </c>
       <c r="Q27" t="n">
-        <v>-17.0124</v>
+        <v>-17.0722</v>
       </c>
       <c r="R27" t="n">
-        <v>12.4759</v>
+        <v>12.5199</v>
       </c>
       <c r="S27" t="n">
-        <v>0.4233999999999998</v>
+        <v>1.9985</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.4366</v>
+        <v>-1.4209</v>
       </c>
       <c r="U27" t="n">
-        <v>1.859900000000001</v>
+        <v>3.4194</v>
       </c>
       <c r="V27" t="n">
-        <v>0.4497</v>
+        <v>0.4582999999999997</v>
       </c>
       <c r="W27" t="n">
-        <v>1.7355</v>
+        <v>1.7205</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.2858</v>
+        <v>-1.2622</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104590_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104590_W15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-1.7206</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104590_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-1.2622</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
